--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/90.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/90.xlsx
@@ -426,13 +426,13 @@
         <v>-9.903523670412051</v>
       </c>
       <c r="E2">
-        <v>-15.55825832963427</v>
+        <v>-13.28016419533562</v>
       </c>
       <c r="F2">
-        <v>-0.4202972000799209</v>
+        <v>-0.50566046093841</v>
       </c>
       <c r="G2">
-        <v>-15.12073747655759</v>
+        <v>-11.65141982849573</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.291749466790231</v>
       </c>
       <c r="E3">
-        <v>-15.77640397953177</v>
+        <v>-14.64607422484721</v>
       </c>
       <c r="F3">
-        <v>-0.4351556261839357</v>
+        <v>-0.5552241677501127</v>
       </c>
       <c r="G3">
-        <v>-14.3358667190161</v>
+        <v>-11.9260825497069</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.613207230007218</v>
       </c>
       <c r="E4">
-        <v>-15.86507150060195</v>
+        <v>-15.09050319243399</v>
       </c>
       <c r="F4">
-        <v>-0.01116488310243949</v>
+        <v>-0.08131351987371002</v>
       </c>
       <c r="G4">
-        <v>-14.12963462937443</v>
+        <v>-11.12348051025707</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.92442238711129</v>
       </c>
       <c r="E5">
-        <v>-16.26577352317067</v>
+        <v>-15.30740804045338</v>
       </c>
       <c r="F5">
-        <v>0.2687636565907918</v>
+        <v>-0.4039419140790474</v>
       </c>
       <c r="G5">
-        <v>-13.52478802771297</v>
+        <v>-11.85242622200366</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.217081064042564</v>
       </c>
       <c r="E6">
-        <v>-16.6373801002401</v>
+        <v>-16.04467983669418</v>
       </c>
       <c r="F6">
-        <v>0.3858997775510588</v>
+        <v>-0.06826756164702061</v>
       </c>
       <c r="G6">
-        <v>-12.79894429713668</v>
+        <v>-10.25931225541342</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.497000755485114</v>
       </c>
       <c r="E7">
-        <v>-17.85624152177461</v>
+        <v>-16.52982431408392</v>
       </c>
       <c r="F7">
-        <v>0.5273128619851707</v>
+        <v>0.01472739680686466</v>
       </c>
       <c r="G7">
-        <v>-12.20753188927358</v>
+        <v>-10.33168409144742</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.765148665857937</v>
       </c>
       <c r="E8">
-        <v>-17.85479693856616</v>
+        <v>-16.87059651163512</v>
       </c>
       <c r="F8">
-        <v>0.7545671752691872</v>
+        <v>0.1844383400880106</v>
       </c>
       <c r="G8">
-        <v>-11.7274134013497</v>
+        <v>-9.707636325658189</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.032712087284367</v>
       </c>
       <c r="E9">
-        <v>-19.13479728767824</v>
+        <v>-17.89613284930818</v>
       </c>
       <c r="F9">
-        <v>0.6373565012426683</v>
+        <v>0.5647782628789868</v>
       </c>
       <c r="G9">
-        <v>-11.70018747483473</v>
+        <v>-9.395167174388538</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.296032092955185</v>
       </c>
       <c r="E10">
-        <v>-19.11932349199403</v>
+        <v>-18.58693797375627</v>
       </c>
       <c r="F10">
-        <v>0.9040874914744979</v>
+        <v>0.481384859704355</v>
       </c>
       <c r="G10">
-        <v>-10.95205384114253</v>
+        <v>-9.10967234817287</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.567427166221791</v>
       </c>
       <c r="E11">
-        <v>-20.26396775301683</v>
+        <v>-18.53247854534003</v>
       </c>
       <c r="F11">
-        <v>1.264261638211723</v>
+        <v>0.8039892312550112</v>
       </c>
       <c r="G11">
-        <v>-9.929922905892553</v>
+        <v>-8.708020410620794</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.852754840416463</v>
       </c>
       <c r="E12">
-        <v>-20.30137294832019</v>
+        <v>-18.78841431083153</v>
       </c>
       <c r="F12">
-        <v>1.63861577815007</v>
+        <v>0.9253798471960564</v>
       </c>
       <c r="G12">
-        <v>-9.708212360582023</v>
+        <v>-7.519597462387683</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.153702358938307</v>
       </c>
       <c r="E13">
-        <v>-21.0426660294798</v>
+        <v>-19.97645040979583</v>
       </c>
       <c r="F13">
-        <v>1.72985879083363</v>
+        <v>1.445268199397443</v>
       </c>
       <c r="G13">
-        <v>-9.248702018640103</v>
+        <v>-8.159423288217086</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.489295562320783</v>
       </c>
       <c r="E14">
-        <v>-21.911834159668</v>
+        <v>-19.97580736648674</v>
       </c>
       <c r="F14">
-        <v>1.400334237999987</v>
+        <v>1.103864858007655</v>
       </c>
       <c r="G14">
-        <v>-9.076345086229027</v>
+        <v>-6.745204581477985</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.8704768750478888</v>
       </c>
       <c r="E15">
-        <v>-22.60654735718471</v>
+        <v>-21.50822485678636</v>
       </c>
       <c r="F15">
-        <v>2.028513404034547</v>
+        <v>1.468454203001801</v>
       </c>
       <c r="G15">
-        <v>-8.405661665428077</v>
+        <v>-6.958539446574159</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.3111075483216937</v>
       </c>
       <c r="E16">
-        <v>-23.11019065089578</v>
+        <v>-21.52494851129669</v>
       </c>
       <c r="F16">
-        <v>1.939725672332885</v>
+        <v>1.809403599054855</v>
       </c>
       <c r="G16">
-        <v>-8.510764865208859</v>
+        <v>-6.232013743616784</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.1705761297206853</v>
       </c>
       <c r="E17">
-        <v>-25.10167766524897</v>
+        <v>-23.7172959902601</v>
       </c>
       <c r="F17">
-        <v>2.339631633177985</v>
+        <v>2.056619910011534</v>
       </c>
       <c r="G17">
-        <v>-8.399967527100531</v>
+        <v>-5.656223800153502</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.5691778379252669</v>
       </c>
       <c r="E18">
-        <v>-23.89036068141124</v>
+        <v>-23.8673107487122</v>
       </c>
       <c r="F18">
-        <v>2.11456420983736</v>
+        <v>2.768928069474412</v>
       </c>
       <c r="G18">
-        <v>-7.934955058472343</v>
+        <v>-5.307189673402602</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.880800449498397</v>
       </c>
       <c r="E19">
-        <v>-25.71974644018587</v>
+        <v>-24.99087043475529</v>
       </c>
       <c r="F19">
-        <v>2.544104186150209</v>
+        <v>2.670513051817414</v>
       </c>
       <c r="G19">
-        <v>-7.835734698114845</v>
+        <v>-4.957291494265952</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.108131373330988</v>
       </c>
       <c r="E20">
-        <v>-26.11510033495152</v>
+        <v>-25.42196304638948</v>
       </c>
       <c r="F20">
-        <v>2.987368553592642</v>
+        <v>2.873322243044817</v>
       </c>
       <c r="G20">
-        <v>-7.396938439612146</v>
+        <v>-5.055995409519323</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.26242172452085</v>
       </c>
       <c r="E21">
-        <v>-26.4156551548406</v>
+        <v>-25.47765421973581</v>
       </c>
       <c r="F21">
-        <v>2.704100036531323</v>
+        <v>3.126424932765789</v>
       </c>
       <c r="G21">
-        <v>-7.032318264462357</v>
+        <v>-5.728304308180054</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.351097526772078</v>
       </c>
       <c r="E22">
-        <v>-26.64638543400541</v>
+        <v>-26.43829752487895</v>
       </c>
       <c r="F22">
-        <v>3.02983232339495</v>
+        <v>3.071343470684039</v>
       </c>
       <c r="G22">
-        <v>-6.634933620110401</v>
+        <v>-5.146068732551813</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.384617628134855</v>
       </c>
       <c r="E23">
-        <v>-26.65221358005329</v>
+        <v>-27.35177677323221</v>
       </c>
       <c r="F23">
-        <v>2.889016491858257</v>
+        <v>2.742688703623335</v>
       </c>
       <c r="G23">
-        <v>-7.127364026894833</v>
+        <v>-4.704832601986671</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.371810561213278</v>
       </c>
       <c r="E24">
-        <v>-27.58955335795295</v>
+        <v>-27.08272201854048</v>
       </c>
       <c r="F24">
-        <v>3.321309961418012</v>
+        <v>3.458474349443165</v>
       </c>
       <c r="G24">
-        <v>-7.380928641384231</v>
+        <v>-4.131843380049613</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.316565819861919</v>
       </c>
       <c r="E25">
-        <v>-27.16881736637431</v>
+        <v>-28.32121437489825</v>
       </c>
       <c r="F25">
-        <v>3.006351420995195</v>
+        <v>3.187606492401755</v>
       </c>
       <c r="G25">
-        <v>-7.081900305004021</v>
+        <v>-4.770348298208847</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.224180823761109</v>
       </c>
       <c r="E26">
-        <v>-28.19134226883227</v>
+        <v>-27.93089161475512</v>
       </c>
       <c r="F26">
-        <v>3.337360408214655</v>
+        <v>3.129035946819413</v>
       </c>
       <c r="G26">
-        <v>-7.079612718036385</v>
+        <v>-5.525924038273328</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.096728753141177</v>
       </c>
       <c r="E27">
-        <v>-27.93399814792438</v>
+        <v>-27.08210161760143</v>
       </c>
       <c r="F27">
-        <v>3.129743372581404</v>
+        <v>3.083182497604849</v>
       </c>
       <c r="G27">
-        <v>-7.236827215150835</v>
+        <v>-4.673187097176777</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.9366416647324691</v>
       </c>
       <c r="E28">
-        <v>-27.14264278660998</v>
+        <v>-27.76847336599601</v>
       </c>
       <c r="F28">
-        <v>3.474614259919311</v>
+        <v>3.373445749015407</v>
       </c>
       <c r="G28">
-        <v>-6.999563726896808</v>
+        <v>-5.465572793092415</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.74515655136142</v>
       </c>
       <c r="E29">
-        <v>-27.14889208074056</v>
+        <v>-27.66128891470846</v>
       </c>
       <c r="F29">
-        <v>3.065839797659839</v>
+        <v>3.215297157942537</v>
       </c>
       <c r="G29">
-        <v>-7.174509505919594</v>
+        <v>-5.594746969489237</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.5200269774314382</v>
       </c>
       <c r="E30">
-        <v>-27.13301072239566</v>
+        <v>-27.92925683563835</v>
       </c>
       <c r="F30">
-        <v>3.360006316272388</v>
+        <v>3.53711955066495</v>
       </c>
       <c r="G30">
-        <v>-6.803698610611367</v>
+        <v>-5.925990224512094</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.261329314215245</v>
       </c>
       <c r="E31">
-        <v>-26.15891784944974</v>
+        <v>-25.89616220210268</v>
       </c>
       <c r="F31">
-        <v>3.069380239939404</v>
+        <v>3.256790081148764</v>
       </c>
       <c r="G31">
-        <v>-7.36176389325739</v>
+        <v>-5.705001378129125</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.03496471985552144</v>
       </c>
       <c r="E32">
-        <v>-26.64494537927097</v>
+        <v>-26.35987341201412</v>
       </c>
       <c r="F32">
-        <v>2.799350690709627</v>
+        <v>3.198184744135505</v>
       </c>
       <c r="G32">
-        <v>-6.587702066901619</v>
+        <v>-5.232136295481785</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.3720077710961731</v>
       </c>
       <c r="E33">
-        <v>-26.02911819896788</v>
+        <v>-25.60585531889296</v>
       </c>
       <c r="F33">
-        <v>2.749178133856866</v>
+        <v>3.09327863951017</v>
       </c>
       <c r="G33">
-        <v>-6.806552300866219</v>
+        <v>-5.607284005446457</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.7476884388464682</v>
       </c>
       <c r="E34">
-        <v>-25.10756468145895</v>
+        <v>-25.56531189110228</v>
       </c>
       <c r="F34">
-        <v>3.124751630612134</v>
+        <v>3.12218203492865</v>
       </c>
       <c r="G34">
-        <v>-7.739036973458274</v>
+        <v>-6.100604948980953</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.165641624620557</v>
       </c>
       <c r="E35">
-        <v>-24.17421448916003</v>
+        <v>-24.83356936162485</v>
       </c>
       <c r="F35">
-        <v>3.323036279085446</v>
+        <v>3.232938070152555</v>
       </c>
       <c r="G35">
-        <v>-8.611776230703102</v>
+        <v>-5.688994890446748</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.621838262889356</v>
       </c>
       <c r="E36">
-        <v>-24.86121116696767</v>
+        <v>-24.38321262156203</v>
       </c>
       <c r="F36">
-        <v>3.346134475745107</v>
+        <v>3.276207013070385</v>
       </c>
       <c r="G36">
-        <v>-8.336842044757708</v>
+        <v>-6.363405985524917</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.107530759690728</v>
       </c>
       <c r="E37">
-        <v>-24.43232392217522</v>
+        <v>-23.92554692445084</v>
       </c>
       <c r="F37">
-        <v>3.402266307693607</v>
+        <v>3.596260013020419</v>
       </c>
       <c r="G37">
-        <v>-8.42032076107597</v>
+        <v>-6.591380082995749</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.617241048850778</v>
       </c>
       <c r="E38">
-        <v>-23.14801246580785</v>
+        <v>-23.1438507981948</v>
       </c>
       <c r="F38">
-        <v>3.650784812207487</v>
+        <v>3.345301138137891</v>
       </c>
       <c r="G38">
-        <v>-8.391879864348091</v>
+        <v>-6.322298941563787</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.136915378235044</v>
       </c>
       <c r="E39">
-        <v>-23.15745433411384</v>
+        <v>-23.56943225696165</v>
       </c>
       <c r="F39">
-        <v>3.46530506704665</v>
+        <v>3.604715987468196</v>
       </c>
       <c r="G39">
-        <v>-7.793171014116436</v>
+        <v>-5.733468759221317</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.653244188228971</v>
       </c>
       <c r="E40">
-        <v>-21.50000567646244</v>
+        <v>-22.68066489126825</v>
       </c>
       <c r="F40">
-        <v>3.537414449460347</v>
+        <v>3.400621170031648</v>
       </c>
       <c r="G40">
-        <v>-8.717369391223695</v>
+        <v>-7.246987279410858</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.156513718044273</v>
       </c>
       <c r="E41">
-        <v>-22.09690383541347</v>
+        <v>-22.02683475709279</v>
       </c>
       <c r="F41">
-        <v>3.436060384258216</v>
+        <v>3.172604758737056</v>
       </c>
       <c r="G41">
-        <v>-8.518498299588597</v>
+        <v>-6.563670816832049</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.630404938593776</v>
       </c>
       <c r="E42">
-        <v>-20.17321260542911</v>
+        <v>-21.15362269961573</v>
       </c>
       <c r="F42">
-        <v>2.855094846713617</v>
+        <v>3.35028956663755</v>
       </c>
       <c r="G42">
-        <v>-8.785755330428421</v>
+        <v>-7.35681131713064</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.068484330930429</v>
       </c>
       <c r="E43">
-        <v>-21.30281780427244</v>
+        <v>-20.45414554744296</v>
       </c>
       <c r="F43">
-        <v>3.607414808466516</v>
+        <v>3.530048606514654</v>
       </c>
       <c r="G43">
-        <v>-9.278099663028831</v>
+        <v>-6.348892553880752</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.466370327588233</v>
       </c>
       <c r="E44">
-        <v>-19.29506903975771</v>
+        <v>-20.87985833195603</v>
       </c>
       <c r="F44">
-        <v>3.132674136452509</v>
+        <v>3.505661470176237</v>
       </c>
       <c r="G44">
-        <v>-9.120444863357658</v>
+        <v>-6.868466123541669</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.815407849025628</v>
       </c>
       <c r="E45">
-        <v>-19.35360862325486</v>
+        <v>-19.33006055841497</v>
       </c>
       <c r="F45">
-        <v>3.181332437692951</v>
+        <v>3.476262711050882</v>
       </c>
       <c r="G45">
-        <v>-8.699141527484468</v>
+        <v>-6.81522593017911</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.119590028367467</v>
       </c>
       <c r="E46">
-        <v>-20.76987528373174</v>
+        <v>-19.10064353671239</v>
       </c>
       <c r="F46">
-        <v>3.132447163784141</v>
+        <v>3.381409673225922</v>
       </c>
       <c r="G46">
-        <v>-9.239839688231474</v>
+        <v>-6.352156751782474</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.379814805156707</v>
       </c>
       <c r="E47">
-        <v>-19.77493784492851</v>
+        <v>-19.24999713795936</v>
       </c>
       <c r="F47">
-        <v>3.105213757049705</v>
+        <v>3.182414285521008</v>
       </c>
       <c r="G47">
-        <v>-8.998368496597033</v>
+        <v>-6.692318616488127</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.594838846449047</v>
       </c>
       <c r="E48">
-        <v>-18.19995269895679</v>
+        <v>-18.19673748241135</v>
       </c>
       <c r="F48">
-        <v>2.831529450838776</v>
+        <v>3.325516411089428</v>
       </c>
       <c r="G48">
-        <v>-8.692189381851998</v>
+        <v>-6.737249340547116</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.774201727246447</v>
       </c>
       <c r="E49">
-        <v>-17.64873778579514</v>
+        <v>-18.16464871559299</v>
       </c>
       <c r="F49">
-        <v>2.721238958095245</v>
+        <v>3.430001705074141</v>
       </c>
       <c r="G49">
-        <v>-9.477139592486433</v>
+        <v>-6.515982408338848</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.920870611545629</v>
       </c>
       <c r="E50">
-        <v>-17.49979174720885</v>
+        <v>-17.37486926323326</v>
       </c>
       <c r="F50">
-        <v>3.057059103190164</v>
+        <v>3.216972116830997</v>
       </c>
       <c r="G50">
-        <v>-10.32338455378047</v>
+        <v>-6.355268664589389</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.039718119399706</v>
       </c>
       <c r="E51">
-        <v>-16.83527441437529</v>
+        <v>-17.02328306975174</v>
       </c>
       <c r="F51">
-        <v>2.908910563403889</v>
+        <v>3.347633820744175</v>
       </c>
       <c r="G51">
-        <v>-9.644404905858108</v>
+        <v>-6.684426275922505</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.144565748038906</v>
       </c>
       <c r="E52">
-        <v>-16.40846121067835</v>
+        <v>-16.51912353000379</v>
       </c>
       <c r="F52">
-        <v>2.786487801678956</v>
+        <v>3.026422763165027</v>
       </c>
       <c r="G52">
-        <v>-10.1704505920483</v>
+        <v>-7.138411317359381</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.235974442121121</v>
       </c>
       <c r="E53">
-        <v>-15.69543033580062</v>
+        <v>-16.75806393254451</v>
       </c>
       <c r="F53">
-        <v>2.601311238987543</v>
+        <v>2.98622872004639</v>
       </c>
       <c r="G53">
-        <v>-9.275371773504471</v>
+        <v>-6.212878790399796</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.323224610822276</v>
       </c>
       <c r="E54">
-        <v>-15.33670726728301</v>
+        <v>-15.90332352054475</v>
       </c>
       <c r="F54">
-        <v>2.692970092107309</v>
+        <v>3.400460466755505</v>
       </c>
       <c r="G54">
-        <v>-9.866996056282085</v>
+        <v>-7.422989122460671</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.417830048312096</v>
       </c>
       <c r="E55">
-        <v>-16.00825279177648</v>
+        <v>-15.59392911939269</v>
       </c>
       <c r="F55">
-        <v>2.695007875918195</v>
+        <v>2.924376182814156</v>
       </c>
       <c r="G55">
-        <v>-9.380498147104028</v>
+        <v>-7.410872525786939</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.516580841290494</v>
       </c>
       <c r="E56">
-        <v>-15.13466487095679</v>
+        <v>-15.26663818896233</v>
       </c>
       <c r="F56">
-        <v>2.454203128659185</v>
+        <v>3.095041405343327</v>
       </c>
       <c r="G56">
-        <v>-10.36327000643761</v>
+        <v>-7.333571287444957</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.628420263454537</v>
       </c>
       <c r="E57">
-        <v>-15.03278326273222</v>
+        <v>-14.35620207514222</v>
       </c>
       <c r="F57">
-        <v>2.397103763584215</v>
+        <v>2.622900150239304</v>
       </c>
       <c r="G57">
-        <v>-10.2221513817351</v>
+        <v>-7.43934652797021</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.756043003474247</v>
       </c>
       <c r="E58">
-        <v>-15.00858309763523</v>
+        <v>-13.35916342439943</v>
       </c>
       <c r="F58">
-        <v>2.738253624548746</v>
+        <v>2.566721929716247</v>
       </c>
       <c r="G58">
-        <v>-9.952861675934162</v>
+        <v>-7.494023498096813</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.892962493677379</v>
       </c>
       <c r="E59">
-        <v>-14.39631529790217</v>
+        <v>-13.13819653519516</v>
       </c>
       <c r="F59">
-        <v>2.366964444000758</v>
+        <v>3.296821764256453</v>
       </c>
       <c r="G59">
-        <v>-10.51716071583063</v>
+        <v>-7.715436094308809</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.045341255631548</v>
       </c>
       <c r="E60">
-        <v>-13.82040661597669</v>
+        <v>-13.65792949705548</v>
       </c>
       <c r="F60">
-        <v>2.790684310941538</v>
+        <v>3.216690471914045</v>
       </c>
       <c r="G60">
-        <v>-10.59272060721896</v>
+        <v>-7.410432223230216</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.205339824382012</v>
       </c>
       <c r="E61">
-        <v>-15.06529770610729</v>
+        <v>-13.60995484341822</v>
       </c>
       <c r="F61">
-        <v>2.175396198429344</v>
+        <v>2.898932049669766</v>
       </c>
       <c r="G61">
-        <v>-10.78053778729843</v>
+        <v>-8.064341109783678</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.364528289580267</v>
       </c>
       <c r="E62">
-        <v>-14.62910150426646</v>
+        <v>-13.29971361762674</v>
       </c>
       <c r="F62">
-        <v>1.96118867173942</v>
+        <v>3.164355876139978</v>
       </c>
       <c r="G62">
-        <v>-10.74240692377711</v>
+        <v>-8.089862105345921</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.525078403841244</v>
       </c>
       <c r="E63">
-        <v>-12.9205444889645</v>
+        <v>-14.29157169410475</v>
       </c>
       <c r="F63">
-        <v>2.192513582440793</v>
+        <v>3.30039534123213</v>
       </c>
       <c r="G63">
-        <v>-10.51139705604676</v>
+        <v>-8.120719700317467</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.670713716691585</v>
       </c>
       <c r="E64">
-        <v>-13.60710190479339</v>
+        <v>-12.37732233242638</v>
       </c>
       <c r="F64">
-        <v>2.261879412016418</v>
+        <v>2.502766996015708</v>
       </c>
       <c r="G64">
-        <v>-10.47966878759839</v>
+        <v>-8.79538239685662</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.797737441131233</v>
       </c>
       <c r="E65">
-        <v>-13.70758421454959</v>
+        <v>-13.15209895039871</v>
       </c>
       <c r="F65">
-        <v>1.898299018518881</v>
+        <v>2.834181883262541</v>
       </c>
       <c r="G65">
-        <v>-10.37582359512253</v>
+        <v>-7.471942159349874</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.905299482807305</v>
       </c>
       <c r="E66">
-        <v>-13.30632518967793</v>
+        <v>-12.76259584405096</v>
       </c>
       <c r="F66">
-        <v>2.117619228818884</v>
+        <v>2.698891262302519</v>
       </c>
       <c r="G66">
-        <v>-10.26964115749594</v>
+        <v>-7.885171074652782</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.980704601119958</v>
       </c>
       <c r="E67">
-        <v>-13.57604563004879</v>
+        <v>-13.91295503927145</v>
       </c>
       <c r="F67">
-        <v>2.067822750766994</v>
+        <v>2.588055703807945</v>
       </c>
       <c r="G67">
-        <v>-10.4417431779005</v>
+        <v>-7.94082465571347</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.026280494574477</v>
       </c>
       <c r="E68">
-        <v>-12.98755231885599</v>
+        <v>-13.84130099504808</v>
       </c>
       <c r="F68">
-        <v>2.04868580702752</v>
+        <v>2.599618056016221</v>
       </c>
       <c r="G68">
-        <v>-10.17041748659291</v>
+        <v>-7.42517408251659</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.03957386439939</v>
       </c>
       <c r="E69">
-        <v>-14.44830670798423</v>
+        <v>-13.34075970603226</v>
       </c>
       <c r="F69">
-        <v>1.816989787729693</v>
+        <v>2.413589931634731</v>
       </c>
       <c r="G69">
-        <v>-8.926685254035194</v>
+        <v>-8.802814571592284</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.01236522666413</v>
       </c>
       <c r="E70">
-        <v>-14.43521941810206</v>
+        <v>-12.92802099955116</v>
       </c>
       <c r="F70">
-        <v>1.865593416721551</v>
+        <v>2.473795674470199</v>
       </c>
       <c r="G70">
-        <v>-9.761512143764287</v>
+        <v>-7.995690326935811</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.950497832780398</v>
       </c>
       <c r="E71">
-        <v>-14.11981573194183</v>
+        <v>-13.20620515784235</v>
       </c>
       <c r="F71">
-        <v>2.233729830934485</v>
+        <v>2.406817199749442</v>
       </c>
       <c r="G71">
-        <v>-9.305779134282677</v>
+        <v>-7.457776334987333</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.848689519449421</v>
       </c>
       <c r="E72">
-        <v>-13.00528129459602</v>
+        <v>-13.94515248946598</v>
       </c>
       <c r="F72">
-        <v>2.111111574502491</v>
+        <v>2.349963031425701</v>
       </c>
       <c r="G72">
-        <v>-9.016420901422679</v>
+        <v>-7.691603476971596</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.7025774110454</v>
       </c>
       <c r="E73">
-        <v>-14.80958383584216</v>
+        <v>-13.65609093660837</v>
       </c>
       <c r="F73">
-        <v>1.826706537364531</v>
+        <v>2.015181659053892</v>
       </c>
       <c r="G73">
-        <v>-8.654919260170884</v>
+        <v>-7.99324714432783</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.519595993746879</v>
       </c>
       <c r="E74">
-        <v>-14.69113706969754</v>
+        <v>-13.9176510668174</v>
       </c>
       <c r="F74">
-        <v>2.013133934834171</v>
+        <v>1.902944502913781</v>
       </c>
       <c r="G74">
-        <v>-8.828782490802327</v>
+        <v>-7.741629130615523</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.292987100545647</v>
       </c>
       <c r="E75">
-        <v>-14.66900188874805</v>
+        <v>-13.18483981747416</v>
       </c>
       <c r="F75">
-        <v>1.891950410743826</v>
+        <v>1.848139715544566</v>
       </c>
       <c r="G75">
-        <v>-8.0299908892682</v>
+        <v>-7.421535792968931</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.024736613589532</v>
       </c>
       <c r="E76">
-        <v>-15.43843490739131</v>
+        <v>-14.19323135255418</v>
       </c>
       <c r="F76">
-        <v>1.733445621687752</v>
+        <v>1.625810874837595</v>
       </c>
       <c r="G76">
-        <v>-8.25152597566515</v>
+        <v>-7.560327104157336</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.721641723712645</v>
       </c>
       <c r="E77">
-        <v>-14.57275370218902</v>
+        <v>-14.86845399794188</v>
       </c>
       <c r="F77">
-        <v>1.888005725171695</v>
+        <v>2.175406138838178</v>
       </c>
       <c r="G77">
-        <v>-7.809922374545148</v>
+        <v>-7.5856560880783</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.380424797097965</v>
       </c>
       <c r="E78">
-        <v>-15.69656698277654</v>
+        <v>-15.13504073429942</v>
       </c>
       <c r="F78">
-        <v>1.720968751866786</v>
+        <v>1.855883294025935</v>
       </c>
       <c r="G78">
-        <v>-7.523311894482745</v>
+        <v>-6.42534960311022</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.010253812058808</v>
       </c>
       <c r="E79">
-        <v>-17.22600926565312</v>
+        <v>-15.10907899281345</v>
       </c>
       <c r="F79">
-        <v>1.695703546081401</v>
+        <v>1.64819998900046</v>
       </c>
       <c r="G79">
-        <v>-7.008750490768286</v>
+        <v>-6.426120960220871</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.617682847361036</v>
       </c>
       <c r="E80">
-        <v>-17.79754344168719</v>
+        <v>-16.91536500567495</v>
       </c>
       <c r="F80">
-        <v>1.739969843352201</v>
+        <v>1.939228651891205</v>
       </c>
       <c r="G80">
-        <v>-7.441859232034517</v>
+        <v>-6.350878881204316</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.203601578311689</v>
       </c>
       <c r="E81">
-        <v>-17.47660143181557</v>
+        <v>-17.09353328703273</v>
       </c>
       <c r="F81">
-        <v>1.651139036545593</v>
+        <v>1.800770353982879</v>
       </c>
       <c r="G81">
-        <v>-7.013775898896899</v>
+        <v>-5.29007746351011</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.782337058796785</v>
       </c>
       <c r="E82">
-        <v>-18.75033437290103</v>
+        <v>-18.60713043935647</v>
       </c>
       <c r="F82">
-        <v>1.458263627212562</v>
+        <v>1.863189494518627</v>
       </c>
       <c r="G82">
-        <v>-6.628865390136917</v>
+        <v>-5.300916189605683</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.358857308269385</v>
       </c>
       <c r="E83">
-        <v>-19.92538733688534</v>
+        <v>-18.82849130579941</v>
       </c>
       <c r="F83">
-        <v>2.192395954269595</v>
+        <v>1.777340810362098</v>
       </c>
       <c r="G83">
-        <v>-6.038806995399377</v>
+        <v>-5.737123601496672</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.936821886887732</v>
       </c>
       <c r="E84">
-        <v>-20.65535017607776</v>
+        <v>-19.67430609553006</v>
       </c>
       <c r="F84">
-        <v>1.718599621094779</v>
+        <v>1.814965257797251</v>
       </c>
       <c r="G84">
-        <v>-5.747776937042048</v>
+        <v>-4.884886552776551</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.531476362720147</v>
       </c>
       <c r="E85">
-        <v>-21.08027953458751</v>
+        <v>-20.52430519524379</v>
       </c>
       <c r="F85">
-        <v>1.596269636518959</v>
+        <v>1.728086084591639</v>
       </c>
       <c r="G85">
-        <v>-5.173238379792611</v>
+        <v>-5.116863099804362</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.144447937658367</v>
       </c>
       <c r="E86">
-        <v>-22.40916928908639</v>
+        <v>-22.12975791433912</v>
       </c>
       <c r="F86">
-        <v>2.014149513270004</v>
+        <v>1.992804142034666</v>
       </c>
       <c r="G86">
-        <v>-5.84760643777877</v>
+        <v>-4.695609422114261</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.783763533620262</v>
       </c>
       <c r="E87">
-        <v>-23.74210297087412</v>
+        <v>-22.44082785087401</v>
       </c>
       <c r="F87">
-        <v>1.737958567298203</v>
+        <v>2.15025856122399</v>
       </c>
       <c r="G87">
-        <v>-5.093123177742249</v>
+        <v>-3.979624496153924</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.459955125580194</v>
       </c>
       <c r="E88">
-        <v>-25.10242486346024</v>
+        <v>-24.2338816626851</v>
       </c>
       <c r="F88">
-        <v>1.86207782546407</v>
+        <v>1.714152944876551</v>
       </c>
       <c r="G88">
-        <v>-5.221535928665038</v>
+        <v>-3.881129145269528</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.175035370931091</v>
       </c>
       <c r="E89">
-        <v>-26.16912502986303</v>
+        <v>-26.28189308960203</v>
       </c>
       <c r="F89">
-        <v>1.951640909054753</v>
+        <v>1.553394996484862</v>
       </c>
       <c r="G89">
-        <v>-4.854350080722314</v>
+        <v>-3.848672556802513</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.942093305921904</v>
       </c>
       <c r="E90">
-        <v>-28.39926262442044</v>
+        <v>-26.8798146836788</v>
       </c>
       <c r="F90">
-        <v>1.792894236717061</v>
+        <v>1.821733019478123</v>
       </c>
       <c r="G90">
-        <v>-4.183471337734548</v>
+        <v>-3.333250411247843</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.768472863899511</v>
       </c>
       <c r="E91">
-        <v>-29.56338158791324</v>
+        <v>-28.68518594479075</v>
       </c>
       <c r="F91">
-        <v>1.69178868173577</v>
+        <v>1.262555201361956</v>
       </c>
       <c r="G91">
-        <v>-4.541136056706328</v>
+        <v>-3.438002693201462</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.657970227305533</v>
       </c>
       <c r="E92">
-        <v>-31.29095140133641</v>
+        <v>-31.76316255696024</v>
       </c>
       <c r="F92">
-        <v>1.40503108117386</v>
+        <v>1.849262981742762</v>
       </c>
       <c r="G92">
-        <v>-4.682284476318695</v>
+        <v>-3.682784430375173</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.622942206064174</v>
       </c>
       <c r="E93">
-        <v>-33.17976206027669</v>
+        <v>-32.44075133001694</v>
       </c>
       <c r="F93">
-        <v>1.853219264458532</v>
+        <v>1.218088439179678</v>
       </c>
       <c r="G93">
-        <v>-5.216947512547609</v>
+        <v>-4.212243289016353</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.661137654496879</v>
       </c>
       <c r="E94">
-        <v>-35.35879808989455</v>
+        <v>-35.98478716587086</v>
       </c>
       <c r="F94">
-        <v>1.905525695740904</v>
+        <v>1.195015093542101</v>
       </c>
       <c r="G94">
-        <v>-5.587950419497113</v>
+        <v>-3.667877043811835</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.771238251263813</v>
       </c>
       <c r="E95">
-        <v>-36.8685641532078</v>
+        <v>-37.21917446054067</v>
       </c>
       <c r="F95">
-        <v>1.751734317206759</v>
+        <v>1.137791473356711</v>
       </c>
       <c r="G95">
-        <v>-4.987685612862001</v>
+        <v>-3.447053724705829</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.955976937242367</v>
       </c>
       <c r="E96">
-        <v>-40.15237802292194</v>
+        <v>-39.54777692968387</v>
       </c>
       <c r="F96">
-        <v>1.441575337515763</v>
+        <v>1.305723083456644</v>
       </c>
       <c r="G96">
-        <v>-5.011614236019853</v>
+        <v>-4.629822261157864</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.197007478346975</v>
       </c>
       <c r="E97">
-        <v>-41.70213277595993</v>
+        <v>-41.1251848092497</v>
       </c>
       <c r="F97">
-        <v>1.501824155456176</v>
+        <v>0.8913472008194415</v>
       </c>
       <c r="G97">
-        <v>-6.058107475893329</v>
+        <v>-4.063606415394156</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.497263176615518</v>
       </c>
       <c r="E98">
-        <v>-45.30042199466273</v>
+        <v>-44.00366402748528</v>
       </c>
       <c r="F98">
-        <v>1.55472866800337</v>
+        <v>0.7132034773777965</v>
       </c>
       <c r="G98">
-        <v>-5.112916929521552</v>
+        <v>-5.397978074271575</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.830235884759688</v>
       </c>
       <c r="E99">
-        <v>-46.26763385135401</v>
+        <v>-46.4185905323997</v>
       </c>
       <c r="F99">
-        <v>1.356018238685019</v>
+        <v>0.646224174289637</v>
       </c>
       <c r="G99">
-        <v>-6.106580483679338</v>
+        <v>-5.180700349438129</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.205092020111605</v>
       </c>
       <c r="E100">
-        <v>-48.86994408223181</v>
+        <v>-48.78343890750029</v>
       </c>
       <c r="F100">
-        <v>0.7917542447156625</v>
+        <v>0.5784181605334834</v>
       </c>
       <c r="G100">
-        <v>-6.27241233083251</v>
+        <v>-6.159701497402483</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.578233134133085</v>
       </c>
       <c r="E101">
-        <v>-50.54140949905545</v>
+        <v>-50.32519637544073</v>
       </c>
       <c r="F101">
-        <v>0.699811261576737</v>
+        <v>0.3367104928054213</v>
       </c>
       <c r="G101">
-        <v>-6.160664866154411</v>
+        <v>-5.543870505641717</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.001805870011527</v>
       </c>
       <c r="E102">
-        <v>-52.71841790443639</v>
+        <v>-52.91581182219373</v>
       </c>
       <c r="F102">
-        <v>0.571701757631585</v>
+        <v>-0.05344309860652065</v>
       </c>
       <c r="G102">
-        <v>-7.223111624981634</v>
+        <v>-5.413911729952088</v>
       </c>
     </row>
   </sheetData>
